--- a/artfynd/A 13105-2026 artfynd.xlsx
+++ b/artfynd/A 13105-2026 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121523087</v>
+        <v>120474569</v>
       </c>
       <c r="B2" t="n">
-        <v>78352</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalarnas län, Dlr</t>
+          <t>Ripfjället, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410313</v>
+        <v>410349</v>
       </c>
       <c r="R2" t="n">
-        <v>6739314</v>
+        <v>6739364</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Anton Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Anton Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121523088</v>
+        <v>120474567</v>
       </c>
       <c r="B3" t="n">
-        <v>78352</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,7 +803,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalarnas län, Dlr</t>
+          <t>Ripfjället, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -867,62 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Anton Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Anton Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121523089</v>
+        <v>120474568</v>
       </c>
       <c r="B4" t="n">
-        <v>56572</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dalarnas län, Dlr</t>
+          <t>Ripfjället, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410238</v>
+        <v>410313</v>
       </c>
       <c r="R4" t="n">
-        <v>6739188</v>
+        <v>6739314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,11 +942,6 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vilande</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -974,62 +954,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Anton Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Anton Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121523086</v>
+        <v>120474566</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalarnas län, Dlr</t>
+          <t>Ripfjället, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410349</v>
+        <v>410238</v>
       </c>
       <c r="R5" t="n">
-        <v>6739364</v>
+        <v>6739188</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,6 +1039,11 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vilande</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1076,12 +1056,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Anton Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Anton Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 13105-2026 artfynd.xlsx
+++ b/artfynd/A 13105-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120474569</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120474567</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120474568</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,8 +1085,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120474566</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>